--- a/最後二週待辦事項/2025_報告順序_志成負責/2026年度慈濟大學「全國經營管理專題競賽-資訊組」報告順序.xlsx
+++ b/最後二週待辦事項/2025_報告順序_志成負責/2026年度慈濟大學「全國經營管理專題競賽-資訊組」報告順序.xlsx
@@ -463,6 +463,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -489,6 +490,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (</t>
@@ -509,6 +511,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>)</t>
@@ -558,6 +561,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>AI</t>
@@ -1334,6 +1338,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (</t>
@@ -1353,6 +1358,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>)</t>
@@ -1559,14 +1565,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>3.現場報告,非花蓮地區選手</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.現場報告,非花蓮地區選手</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>智藥守護者：AI用藥與情緒感知系統</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1650,6 +1648,16 @@
   <si>
     <t>2.線上報告
 (非花蓮地區選手)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.現場報告,
+非花蓮地區選手</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.現場報告,
+非花蓮地區選手</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1671,6 +1679,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1678,6 +1687,7 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2265,10 +2275,10 @@
     </row>
     <row r="2" spans="1:7" ht="39.6">
       <c r="A2" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>139</v>
@@ -2292,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D3" s="12">
         <v>0.41666666666666669</v>
@@ -2407,10 +2417,10 @@
     </row>
     <row r="9" spans="1:7" ht="39.6">
       <c r="A9" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>139</v>
@@ -2422,7 +2432,7 @@
         <v>242</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G9" s="8"/>
     </row>
@@ -2549,10 +2559,10 @@
     </row>
     <row r="16" spans="1:7" ht="39.6">
       <c r="A16" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C16" s="35" t="s">
         <v>139</v>
@@ -2564,7 +2574,7 @@
         <v>242</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G16" s="8"/>
     </row>
@@ -2622,7 +2632,7 @@
         <v>0.58055555555555549</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F19" s="42" t="s">
         <v>248</v>
@@ -2642,10 +2652,10 @@
         <v>0.58958333333333324</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G20" s="8"/>
     </row>
@@ -2662,10 +2672,10 @@
         <v>0.59861111111111098</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G21" s="8"/>
     </row>
@@ -2682,19 +2692,19 @@
         <v>0.60763888888888873</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:7" ht="39.6">
       <c r="A23" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C23" s="35" t="s">
         <v>139</v>
@@ -2706,7 +2716,7 @@
         <v>242</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G23" s="8"/>
     </row>
@@ -2724,10 +2734,10 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G24" s="8"/>
     </row>
@@ -2744,10 +2754,10 @@
         <v>0.62361111111111112</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G25" s="8"/>
     </row>
@@ -2760,14 +2770,14 @@
         <v>119</v>
       </c>
       <c r="D26" s="12">
-        <f t="shared" ref="D26:D29" si="3">D25 + TIME(0,13,0)</f>
+        <f t="shared" ref="D26:D28" si="3">D25 + TIME(0,13,0)</f>
         <v>0.63263888888888886</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G26" s="8"/>
     </row>
@@ -2784,10 +2794,10 @@
         <v>0.64166666666666661</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G27" s="8"/>
     </row>
@@ -2807,7 +2817,7 @@
         <v>223</v>
       </c>
       <c r="F28" s="33" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="G28" s="8"/>
     </row>
@@ -2827,7 +2837,7 @@
         <v>241</v>
       </c>
       <c r="F29" s="33" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="G29" s="8"/>
     </row>
